--- a/artfynd/A 13766-2024 artfynd.xlsx
+++ b/artfynd/A 13766-2024 artfynd.xlsx
@@ -1103,7 +1103,7 @@
         <v>121340272</v>
       </c>
       <c r="B6" t="n">
-        <v>99326</v>
+        <v>99336</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>

--- a/artfynd/A 13766-2024 artfynd.xlsx
+++ b/artfynd/A 13766-2024 artfynd.xlsx
@@ -1103,7 +1103,7 @@
         <v>121340272</v>
       </c>
       <c r="B6" t="n">
-        <v>99336</v>
+        <v>99349</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>

--- a/artfynd/A 13766-2024 artfynd.xlsx
+++ b/artfynd/A 13766-2024 artfynd.xlsx
@@ -1103,7 +1103,7 @@
         <v>121340272</v>
       </c>
       <c r="B6" t="n">
-        <v>99349</v>
+        <v>99350</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>

--- a/artfynd/A 13766-2024 artfynd.xlsx
+++ b/artfynd/A 13766-2024 artfynd.xlsx
@@ -1103,7 +1103,7 @@
         <v>121340272</v>
       </c>
       <c r="B6" t="n">
-        <v>99350</v>
+        <v>99353</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>

--- a/artfynd/A 13766-2024 artfynd.xlsx
+++ b/artfynd/A 13766-2024 artfynd.xlsx
@@ -1103,7 +1103,7 @@
         <v>121340272</v>
       </c>
       <c r="B6" t="n">
-        <v>99353</v>
+        <v>99359</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>

--- a/artfynd/A 13766-2024 artfynd.xlsx
+++ b/artfynd/A 13766-2024 artfynd.xlsx
@@ -1103,7 +1103,7 @@
         <v>121340272</v>
       </c>
       <c r="B6" t="n">
-        <v>99359</v>
+        <v>99360</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>

--- a/artfynd/A 13766-2024 artfynd.xlsx
+++ b/artfynd/A 13766-2024 artfynd.xlsx
@@ -1103,7 +1103,7 @@
         <v>121340272</v>
       </c>
       <c r="B6" t="n">
-        <v>99360</v>
+        <v>99368</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>

--- a/artfynd/A 13766-2024 artfynd.xlsx
+++ b/artfynd/A 13766-2024 artfynd.xlsx
@@ -1103,11 +1103,11 @@
         <v>121340272</v>
       </c>
       <c r="B6" t="n">
-        <v>99368</v>
+        <v>99430</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">

--- a/artfynd/A 13766-2024 artfynd.xlsx
+++ b/artfynd/A 13766-2024 artfynd.xlsx
@@ -1103,7 +1103,7 @@
         <v>121340272</v>
       </c>
       <c r="B6" t="n">
-        <v>99430</v>
+        <v>99440</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>

--- a/artfynd/A 13766-2024 artfynd.xlsx
+++ b/artfynd/A 13766-2024 artfynd.xlsx
@@ -1103,7 +1103,7 @@
         <v>121340272</v>
       </c>
       <c r="B6" t="n">
-        <v>99440</v>
+        <v>99452</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>

--- a/artfynd/A 13766-2024 artfynd.xlsx
+++ b/artfynd/A 13766-2024 artfynd.xlsx
@@ -1103,7 +1103,7 @@
         <v>121340272</v>
       </c>
       <c r="B6" t="n">
-        <v>99452</v>
+        <v>99457</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>

--- a/artfynd/A 13766-2024 artfynd.xlsx
+++ b/artfynd/A 13766-2024 artfynd.xlsx
@@ -1103,7 +1103,7 @@
         <v>121340272</v>
       </c>
       <c r="B6" t="n">
-        <v>99457</v>
+        <v>99466</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1117,11 +1117,6 @@
       </c>
       <c r="E6" t="n">
         <v>2082</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Skogsrör</t>
-        </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>

--- a/artfynd/A 13766-2024 artfynd.xlsx
+++ b/artfynd/A 13766-2024 artfynd.xlsx
@@ -1103,7 +1103,7 @@
         <v>121340272</v>
       </c>
       <c r="B6" t="n">
-        <v>99466</v>
+        <v>99479</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1117,6 +1117,11 @@
       </c>
       <c r="E6" t="n">
         <v>2082</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Skogsrör</t>
+        </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>

--- a/artfynd/A 13766-2024 artfynd.xlsx
+++ b/artfynd/A 13766-2024 artfynd.xlsx
@@ -1103,7 +1103,7 @@
         <v>121340272</v>
       </c>
       <c r="B6" t="n">
-        <v>99479</v>
+        <v>99492</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>

--- a/artfynd/A 13766-2024 artfynd.xlsx
+++ b/artfynd/A 13766-2024 artfynd.xlsx
@@ -1103,7 +1103,7 @@
         <v>121340272</v>
       </c>
       <c r="B6" t="n">
-        <v>99492</v>
+        <v>99495</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>

--- a/artfynd/A 13766-2024 artfynd.xlsx
+++ b/artfynd/A 13766-2024 artfynd.xlsx
@@ -1103,7 +1103,7 @@
         <v>121340272</v>
       </c>
       <c r="B6" t="n">
-        <v>99495</v>
+        <v>99496</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>

--- a/artfynd/A 13766-2024 artfynd.xlsx
+++ b/artfynd/A 13766-2024 artfynd.xlsx
@@ -1103,7 +1103,7 @@
         <v>121340272</v>
       </c>
       <c r="B6" t="n">
-        <v>99496</v>
+        <v>99499</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
